--- a/0-0-面试八股.xlsx
+++ b/0-0-面试八股.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145CBB79-0081-8140-864A-4D19D4675418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF713DF5-79C9-DC42-A67D-86B69D1D5E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="620" windowWidth="28040" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>名称</t>
   </si>
@@ -361,45 +361,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -485,6 +446,65 @@
           <color indexed="64"/>
         </horizontal>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -522,26 +542,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -561,15 +561,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7396C1F5-49E2-7641-B1E1-EFCF0E5BC0FF}" name="表1" displayName="表1" ref="A1:D16" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6" headerRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7396C1F5-49E2-7641-B1E1-EFCF0E5BC0FF}" name="表1" displayName="表1" ref="A1:D16" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5">
   <autoFilter ref="A1:D16" xr:uid="{7396C1F5-49E2-7641-B1E1-EFCF0E5BC0FF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{31804628-DC26-E143-8EB5-44E04F53DB85}" name="No." dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{31804628-DC26-E143-8EB5-44E04F53DB85}" name="No." dataDxfId="3">
       <calculatedColumnFormula xml:space="preserve"> ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E8E0D280-D5C8-E741-9148-1DC7B31FAB70}" name="类型" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{C087E8E9-979C-2C41-AF18-84A8736910E4}" name="名称" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E014EEAE-2614-0A4D-8A9F-6CB55F39CE0F}" name="状态" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{E8E0D280-D5C8-E741-9148-1DC7B31FAB70}" name="类型" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{C087E8E9-979C-2C41-AF18-84A8736910E4}" name="名称" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{E014EEAE-2614-0A4D-8A9F-6CB55F39CE0F}" name="状态" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -872,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="14.59765625" customWidth="1"/>
@@ -881,7 +881,7 @@
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="12.75" customHeight="1" thickBot="1">
+    <row r="1" spans="1:4" ht="12.75" customHeight="1" thickBot="1">
       <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="12.75" customHeight="1">
+    <row r="2" spans="1:4" ht="12.75" customHeight="1">
       <c r="A2" s="5">
         <f xml:space="preserve"> ROW()-1</f>
         <v>1</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:6" ht="12.75" customHeight="1">
+    <row r="3" spans="1:4" ht="12.75" customHeight="1">
       <c r="A3" s="6">
         <f t="shared" ref="A3:A16" si="0" xml:space="preserve"> ROW()-1</f>
         <v>2</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="D3" s="9"/>
     </row>
-    <row r="4" spans="1:6" ht="12.75" customHeight="1">
+    <row r="4" spans="1:4" ht="12.75" customHeight="1">
       <c r="A4" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:6" ht="12.75" customHeight="1">
+    <row r="5" spans="1:4" ht="12.75" customHeight="1">
       <c r="A5" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:6" ht="12.75" customHeight="1">
+    <row r="6" spans="1:4" ht="12.75" customHeight="1">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -962,7 +962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="12.75" customHeight="1">
+    <row r="7" spans="1:4" ht="12.75" customHeight="1">
       <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="12.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:4" ht="12.75" customHeight="1">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -987,9 +987,8 @@
         <v>16</v>
       </c>
       <c r="D8" s="9"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="12.75" customHeight="1">
+    </row>
+    <row r="9" spans="1:4" ht="12.75" customHeight="1">
       <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1002,7 +1001,7 @@
       </c>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="12.75" customHeight="1">
+    <row r="10" spans="1:4" ht="12.75" customHeight="1">
       <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1015,7 +1014,7 @@
       </c>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="12.75" customHeight="1">
+    <row r="11" spans="1:4" ht="12.75" customHeight="1">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1028,7 +1027,7 @@
       </c>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="12.75" customHeight="1">
+    <row r="12" spans="1:4" ht="12.75" customHeight="1">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1043,7 +1042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="12.75" customHeight="1">
+    <row r="13" spans="1:4" ht="12.75" customHeight="1">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1056,7 +1055,7 @@
       </c>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:6" ht="12.75" customHeight="1">
+    <row r="14" spans="1:4" ht="12.75" customHeight="1">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1069,7 +1068,7 @@
       </c>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="12.75" customHeight="1">
+    <row r="15" spans="1:4" ht="12.75" customHeight="1">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1080,9 +1079,11 @@
       <c r="C15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" ht="12.75" customHeight="1" thickBot="1">
+      <c r="D15" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12.75" customHeight="1" thickBot="1">
       <c r="A16" s="7">
         <f t="shared" si="0"/>
         <v>15</v>
